--- a/table/source/Ability.xlsx
+++ b/table/source/Ability.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,17 +454,32 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
@@ -501,22 +516,37 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>cast_time_ticks</t>
+          <t>startup_ticks</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>active_ticks</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>recovery_ticks</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>targeting_mode</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>range</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>produces_effect_id</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>motion_speed</t>
         </is>
       </c>
     </row>
@@ -548,16 +578,74 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dash</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>전방 대시</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/table/source/Ability.xlsx
+++ b/table/source/Ability.xlsx
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
